--- a/Categoría/ULA_Categoría.xlsx
+++ b/Categoría/ULA_Categoría.xlsx
@@ -833,13 +833,13 @@
         <v>0.5434335736377101</v>
       </c>
       <c r="C2" s="2">
-        <v>112.2262160580291</v>
+        <v>111.0917574884164</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>0.6098749364825251</v>
+        <v>0.6037099077362396</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1969,7 +1969,7 @@
         <v>73</v>
       </c>
       <c r="B69" s="2">
-        <v>0.3510118757025276</v>
+        <v>0.3510118757025275</v>
       </c>
       <c r="C69" s="2">
         <v>115.3272131315082</v>
@@ -1978,7 +1978,7 @@
         <v>6</v>
       </c>
       <c r="E69" s="2">
-        <v>0.4048122140083585</v>
+        <v>0.4048122140083584</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -2003,7 +2003,7 @@
         <v>75</v>
       </c>
       <c r="B71" s="2">
-        <v>0.8759865797997735</v>
+        <v>0.8759865797997733</v>
       </c>
       <c r="C71" s="2">
         <v>115.2660548810867</v>
@@ -2904,7 +2904,7 @@
         <v>128</v>
       </c>
       <c r="B124" s="2">
-        <v>2.67229302731753</v>
+        <v>2.672293027317531</v>
       </c>
       <c r="C124" s="2">
         <v>125.8821724526704</v>
@@ -2921,7 +2921,7 @@
         <v>129</v>
       </c>
       <c r="B125" s="2">
-        <v>6.489204867751228</v>
+        <v>6.489204867751229</v>
       </c>
       <c r="C125" s="2">
         <v>114.0308392774936</v>
@@ -2930,7 +2930,7 @@
         <v>6</v>
       </c>
       <c r="E125" s="2">
-        <v>7.399694773132697</v>
+        <v>7.399694773132698</v>
       </c>
     </row>
     <row r="126" spans="1:5">
